--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/TransMonthreport.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/TransMonthreport.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\BS\BS3.0\codes\codegit\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F66FAD3-C800-4937-B906-07FE14037C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="8820" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="产品存续情况" sheetId="4" r:id="rId1"/>
@@ -912,14 +918,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,24 +931,28 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -956,153 +960,25 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1115,194 +991,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="23">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1325,403 +1015,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1736,61 +1039,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1798,133 +1053,74 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="4">
+    <cellStyle name="?鹎%U龡&amp;H?_x0008__x001c__x001c_?_x0007__x0001__x0001_" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="?鹎%U龡&amp;H?_x0008__x001C__x001C_?_x0007__x0001__x0001_" xfId="49"/>
-    <cellStyle name="常规 2" xfId="50"/>
-    <cellStyle name="常规 3" xfId="51"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2211,710 +1407,700 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="27.625" customWidth="1"/>
-    <col min="3" max="3" width="25.625" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="6" width="27.875" customWidth="1"/>
-    <col min="7" max="7" width="65.25" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="25.6328125" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" customWidth="1"/>
+    <col min="5" max="6" width="27.90625" customWidth="1"/>
+    <col min="7" max="7" width="65.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:7">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:7" ht="23" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:7">
-      <c r="A2" s="27" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:7">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="13" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:7">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="17" t="s">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:7">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:7">
-      <c r="A6" s="18"/>
-      <c r="B6" s="22" t="s">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="21"/>
+      <c r="D6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:7">
-      <c r="A7" s="33"/>
-      <c r="B7" s="23" t="s">
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="32" t="s">
+      <c r="C7" s="22"/>
+      <c r="D7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:7">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:7">
-      <c r="A9" s="18"/>
-      <c r="B9" s="31" t="s">
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:7">
-      <c r="A10" s="18"/>
-      <c r="B10" s="31" t="s">
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:7">
-      <c r="A11" s="18"/>
-      <c r="B11" s="31" t="s">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32" t="s">
+      <c r="C11" s="21"/>
+      <c r="D11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:7">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34" t="s">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="32" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:7">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:7">
-      <c r="A14" s="18"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="36" t="s">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" ht="28.5" spans="1:7">
-      <c r="A15" s="18"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="38" t="s">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" ht="28.5" spans="1:7">
-      <c r="A16" s="18"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="38" t="s">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:7">
-      <c r="A17" s="18"/>
-      <c r="B17" s="35" t="s">
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="14" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:7">
-      <c r="A18" s="18"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="40" t="s">
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:7">
-      <c r="A19" s="18"/>
-      <c r="B19" s="41" t="s">
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="32" t="s">
+      <c r="C19" s="22"/>
+      <c r="D19" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="14" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:7">
-      <c r="A20" s="42" t="s">
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:7">
-      <c r="A21" s="42"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="22" t="s">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F21" s="32" t="s">
+      <c r="F21" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="14" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:7">
-      <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="22" t="s">
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="F22" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="14" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="1:7">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="22" t="s">
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:7">
-      <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="22" t="s">
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="1:7">
-      <c r="A25" s="42"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="23" t="s">
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="G25" s="32" t="s">
+      <c r="G25" s="14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="26" ht="14.25" spans="1:7">
-      <c r="A26" s="42"/>
-      <c r="B26" s="46" t="s">
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="32" t="s">
+      <c r="G26" s="14" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="1:7">
-      <c r="A27" s="42"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="22" t="s">
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="F27" s="32" t="s">
+      <c r="F27" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="14" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="28" ht="14.25" spans="1:7">
-      <c r="A28" s="42"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="22" t="s">
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="G28" s="32" t="s">
+      <c r="G28" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="1:7">
-      <c r="A29" s="42"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="22" t="s">
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="32" t="s">
+      <c r="G29" s="14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="30" ht="14.25" spans="1:7">
-      <c r="A30" s="42"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="22" t="s">
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="G30" s="32" t="s">
+      <c r="G30" s="14" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="1:7">
-      <c r="A31" s="42"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="22" t="s">
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="F31" s="32" t="s">
+      <c r="F31" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:7">
-      <c r="A32" s="42"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="22" t="s">
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="1:7">
-      <c r="A33" s="42"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="22" t="s">
+    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="F33" s="32" t="s">
+      <c r="F33" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="14" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="34" ht="14.25" spans="1:7">
-      <c r="A34" s="42"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="23" t="s">
+    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="F34" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="14" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="1:7">
-      <c r="A35" s="50"/>
-      <c r="B35" s="23" t="s">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="32" t="s">
+      <c r="C35" s="22"/>
+      <c r="D35" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="F35" s="32" t="s">
+      <c r="F35" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="14" t="s">
         <v>179</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A12"/>
@@ -2924,511 +2110,519 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="B26:B34"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="A3:C4"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.75" customWidth="1"/>
-    <col min="2" max="2" width="52.125" customWidth="1"/>
-    <col min="3" max="3" width="46.75" customWidth="1"/>
-    <col min="4" max="4" width="61.75" customWidth="1"/>
+    <col min="1" max="1" width="32.7265625" customWidth="1"/>
+    <col min="2" max="2" width="52.08984375" customWidth="1"/>
+    <col min="3" max="3" width="46.7265625" customWidth="1"/>
+    <col min="4" max="4" width="61.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" spans="1:4">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:4" ht="23" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" ht="14.25" spans="1:4">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:4">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:4">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16" t="s">
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="8" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:4">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="10" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:4">
-      <c r="A6" s="18"/>
-      <c r="B6" s="21" t="s">
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="10" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:4">
-      <c r="A7" s="18"/>
-      <c r="B7" s="21" t="s">
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="10" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:4">
-      <c r="A8" s="18"/>
-      <c r="B8" s="21" t="s">
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="10" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:4">
-      <c r="A9" s="18"/>
-      <c r="B9" s="21" t="s">
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="10" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:4">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="10" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:4">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:4">
-      <c r="A12" s="18"/>
-      <c r="B12" s="22" t="s">
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:4">
-      <c r="A13" s="18"/>
-      <c r="B13" s="22" t="s">
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:4">
-      <c r="A14" s="18"/>
-      <c r="B14" s="22" t="s">
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:4">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:4">
-      <c r="A16" s="18"/>
-      <c r="B16" s="22" t="s">
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="10" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:4">
-      <c r="A17" s="18"/>
-      <c r="B17" s="22" t="s">
+    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
+      <c r="B17" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:4">
-      <c r="A18" s="18"/>
-      <c r="B18" s="23" t="s">
+    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="27" t="s">
         <v>225</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="10" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:4">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19" t="s">
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
+      <c r="B19" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="10" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:4">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="10" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:4">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="10" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="22" t="s">
+    <row r="22" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
+      <c r="B22" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="10" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="1:4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="22" t="s">
+    <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="B23" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="10" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="19" t="s">
+    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="10" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="1:4">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="10" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="26" ht="14.25" spans="1:4">
-      <c r="A26" s="18"/>
-      <c r="B26" s="21" t="s">
+    <row r="26" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
+      <c r="B26" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="10" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="1:4">
-      <c r="A27" s="18"/>
-      <c r="B27" s="21" t="s">
+    <row r="27" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
+      <c r="B27" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="28" ht="14.25" spans="1:4">
-      <c r="A28" s="18"/>
-      <c r="B28" s="21" t="s">
+    <row r="28" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="1:4">
-      <c r="A29" s="18"/>
-      <c r="B29" s="21" t="s">
+    <row r="29" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
+      <c r="B29" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="30" ht="14.25" spans="1:4">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19" t="s">
+    <row r="30" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="10" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="1:4">
-      <c r="A31" s="25" t="s">
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="10" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:4">
-      <c r="A32" s="25"/>
-      <c r="B32" s="21" t="s">
+    <row r="32" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="10" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="1:4">
-      <c r="A33" s="25"/>
-      <c r="B33" s="21" t="s">
+    <row r="33" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="10" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="34" ht="14.25" spans="1:4">
-      <c r="A34" s="25"/>
-      <c r="B34" s="21" t="s">
+    <row r="34" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
+      <c r="B34" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="10" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="1:4">
-      <c r="A35" s="25"/>
-      <c r="B35" s="21" t="s">
+    <row r="35" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
+      <c r="B35" s="29" t="s">
         <v>280</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="10" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="1:4">
-      <c r="A36" s="25"/>
-      <c r="B36" s="21" t="s">
+    <row r="36" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="10" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="37" ht="14.25" spans="1:4">
-      <c r="A37" s="26"/>
-      <c r="B37" s="19" t="s">
+    <row r="37" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
+      <c r="B37" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="10" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="38" ht="14.25" spans="1:4">
-      <c r="A38" s="18" t="s">
+    <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="10" t="s">
         <v>291</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="A31:A37"/>
+    <mergeCell ref="A3:B4"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:A10"/>
     <mergeCell ref="A11:A19"/>
     <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A25:A30"/>
-    <mergeCell ref="A31:A37"/>
-    <mergeCell ref="A3:B4"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
-    <col min="2" max="2" width="35.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6328125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:3">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>292</v>
       </c>
@@ -3437,7 +2631,7 @@
       </c>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="14.25" spans="1:3">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>294</v>
       </c>
@@ -3446,7 +2640,7 @@
       </c>
       <c r="C2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:3">
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>295</v>
       </c>
@@ -3455,13 +2649,13 @@
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="14.25" spans="1:3">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>